--- a/reports/acdr2026_staff_deployment/ACDR2026_持参物分担一覧_1007案.xlsx
+++ b/reports/acdr2026_staff_deployment/ACDR2026_持参物分担一覧_1007案.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14856" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="持参物分担（案）" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="職員の便" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="持参物分担（案）" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="職員の便" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>ビデオカメラ（ソニー）＋三脚＋HDMI ケーブル・予備バッテリー・SD</t>
+          <t>ビデオカメラ（ソニー）＋三脚＋HDMI ケーブル 10m・予備バッテリー・SD</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>28〜29 日 Zoom 配信（HDMI で業者スイッチャーへ）</t>
+          <t>28〜29 日 Zoom 配信。会場の後方中央に置き、10m の HDMI で AV 卓の Zoom PC へ（10/7 Sylvia さんと調整中）</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>神戸の機材は神戸発の職員が運ぶ（荒木田は羽田発）。カメラ本体は手荷物、三脚は預け入れ。乗継ぎがあるので三脚はケースに入れて名札を付ける。業者とのオンライン会議で接続を確認してから持込内容を確定</t>
+          <t>神戸の機材は神戸発の職員が運ぶ（荒木田は羽田発）。カメラ本体は手荷物、三脚は預け入れ。乗継ぎがあるので三脚はケースに入れて名札を付ける。業者とのオンライン会議で接続を確認してから持込内容を確定 10/7: Sylvia さんの指摘で設置場所を AV 卓脇から後方中央に変更する方向（RT の発言者は U 字の席から話すため）。後方中央から AV 卓まで 10m を超える場合は業者に延長を依頼。中央に置く場合はカメラ横に操作者が要る（荒木田が Opening・Closing の進行と重なる時間は交代）。</t>
         </is>
       </c>
     </row>
